--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:05</t>
+    <t xml:space="preserve">2026-10-05 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -590,7 +590,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1294389.62</v>
+        <v>1294389.63</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1291904.12</v>
+        <v>1291904.13</v>
       </c>
     </row>
     <row r="9">
